--- a/results/job_matches_2026-08-28.xlsx
+++ b/results/job_matches_2026-08-28.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G101"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer – Hadoop / AWS EMR, Spark + Scala &amp; Kafka</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Virtues</t>
+          <t>Symmetry Lending</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, IAM, GCP, BigQuery, Hadoop</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ac65065c216ba1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc487e12b46c0c21</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer, Software</t>
+          <t>Full-Stack Developer (Java, AWS)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>InfoCepts</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Azure, Blob Storage, Scala, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9610995ca15527f1</t>
+          <t>https://www.indeed.com/viewjob?jk=a73e32f595e74960</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III: Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, clustering keys, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6002f30e875ad9c5</t>
+          <t>https://www.indeed.com/viewjob?jk=83af2bafae6adab2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer Stf - E4</t>
+          <t>Software Engineer III: Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Bragg, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Kinesis, S3, ECS, RDS, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=862b277963d1774e</t>
+          <t>https://www.indeed.com/viewjob?jk=6002f30e875ad9c5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer Stf - E4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Bragg, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d9ffe640eb96ce</t>
+          <t>https://www.indeed.com/viewjob?jk=862b277963d1774e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Back End Go Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cc2fd48ea54d930</t>
+          <t>https://www.indeed.com/viewjob?jk=75d9ffe640eb96ce</t>
         </is>
       </c>
     </row>
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Infrastructure Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chervon North America</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, S3, ECS, IAM, Unity Catalog, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Scala, Oracle, MySQL, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb602e905cf8e618</t>
+          <t>https://www.indeed.com/viewjob?jk=bea2b6207934b593</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer - Medical Billing Automation SaaS platform ( Python / AI / LLM / EDI )</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Relentless Talent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a0d061adef57ed</t>
+          <t>https://www.indeed.com/viewjob?jk=572fb82d8ddec77b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chervon North America</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, Scala, Oracle, MySQL, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,94 +916,94 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bea2b6207934b593</t>
+          <t>https://www.indeed.com/viewjob?jk=11cb1d159dbef75d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Solution Architect</t>
+          <t>Data Engineering Winter/Spring Co-Op (Jan-June '27)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CLS Living</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Scala</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67a77c894dfb7cd7</t>
+          <t>https://www.indeed.com/viewjob?jk=efe070deedac1b9a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineering Summer/Fall Co-Op (June - Dec '27)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Skyworks Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, Data Factory, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Cloud Storage, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11cb1d159dbef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=8446a0ee2fc12124</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Data Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>APLOMB Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Hadoop, HDFS, Hive, Spark</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cadd1b7c846571a5</t>
+          <t>https://www.indeed.com/viewjob?jk=cd0f74f20f4d3d53</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, RDS, Spark, Scala, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cecaeb7f30f5319a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb582296830c7c0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Senior Engineer 2, Merchandising (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,42 +1081,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, RDS, Scala, Kafka, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd0f74f20f4d3d53</t>
+          <t>https://www.indeed.com/viewjob?jk=55921bc34dbfb58a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>Data Engineer / Dev Ops Engineer (Entry-level)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fb582296830c7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c74dd3c01bed4e6</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer / Dev Ops Engineer (Entry-level)</t>
+          <t>Senior Database Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Inadev Corporation</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Scala, Snowflake, PostgreSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c74dd3c01bed4e6</t>
+          <t>https://www.indeed.com/viewjob?jk=44742e2d35b42b9d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate, Software Engineer - SMA Solutions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tillys</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, GCP, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Azure, GCP, MySQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cff22505a47f4228</t>
+          <t>https://www.indeed.com/viewjob?jk=1d538b0abcf938eb</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Database Developer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Inadev Corporation</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, PostgreSQL, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,94 +1231,94 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44742e2d35b42b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=01957aab12acd0bb</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Ziff Davis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Kinesis, RDS, Spark, Scala, Kafka, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e40611058ee4416</t>
+          <t>https://www.indeed.com/viewjob?jk=be21e3c48dd456fe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Hive, Spark, Scala, Kafka, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01957aab12acd0bb</t>
+          <t>https://www.indeed.com/viewjob?jk=7a530d898f0f57a3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Data Platform)</t>
+          <t>.Net Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cerebras Systems</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df71053024d6fe55</t>
+          <t>https://www.indeed.com/viewjob?jk=d8b91a8e3ad02664</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Integration Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Northwood Investors</t>
+          <t>Department of Social Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,59 +1371,59 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2347d9cb82b32b</t>
+          <t>https://www.indeed.com/viewjob?jk=60e35cd3d7a76f2b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Department of Social Services</t>
+          <t>AnewHealth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, SQL Server, MongoDB, Cassandra, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60e35cd3d7a76f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=cd63cf544b64f9bc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Oliver Wyman Vector - DevOps Engineer (AWS &amp; Cybersecurity)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NationsBenefits</t>
+          <t>Marsh</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Scala, Kafka, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0137050565978d38</t>
+          <t>https://www.indeed.com/viewjob?jk=5025df0e29ed9ee5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Oliver Wyman Vector - DevOps Engineer (AWS &amp; Cybersecurity)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marsh</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5025df0e29ed9ee5</t>
+          <t>https://www.indeed.com/viewjob?jk=093103681f1f9c6b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>AI Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=093103681f1f9c6b</t>
+          <t>https://www.indeed.com/viewjob?jk=fc5faddbf4679157</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, S3, RDS, Azure, GCP, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d4d4ff843dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=3dcced776a5fe5e2</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AWS Architect</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SQS, SNS, API Gateway, ECS, IAM</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be4021803dd89422</t>
+          <t>https://www.indeed.com/viewjob?jk=408197639f35cd58</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,164 +1651,164 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed654d6987db5d87</t>
+          <t>https://www.indeed.com/viewjob?jk=429cbc163ce4bf5f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Analytics Engineer, Finance</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Boston Scientific</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Marlboro, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429cbc163ce4bf5f</t>
+          <t>https://www.indeed.com/viewjob?jk=38276618e771db29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Database Administrator III</t>
+          <t>Infrastructure Solutions Architect – Contract Position</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>BranCore Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling, Dimensional Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba70fd5fe4fff929</t>
+          <t>https://www.indeed.com/viewjob?jk=007f823364fb3e0d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Apollo Technology Solutions LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408197639f35cd58</t>
+          <t>https://www.indeed.com/viewjob?jk=51bd2a53e1c64d96</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior MLOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Guild Mortgage Company LLC</t>
+          <t>Hard Rock International</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, MySQL, MongoDB, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cfce3fc392b166a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f714260334a172e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Quality Data Scientist - Electrical Systems &amp; Field Quality Engineering</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7-Eleven</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,112 +1816,112 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Power BI, Tableau, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e74e8ed1040b80da</t>
+          <t>https://www.indeed.com/viewjob?jk=de315437102e29bb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineer, AI Support</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MetLife Legal Plans</t>
+          <t>Insurance Institute for Business and Home Safety</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richburg, SC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Spark, Data Modeling, ETL, dbt, Tableau</t>
+          <t>AWS, Azure, Spark, Scala, NoSQL, Data Modeling, ETL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b49427628ff5f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=78dd04fa52447364</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data, Analytics &amp; Cloud Engineering Consultant</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Kenway Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57257275c845106a</t>
+          <t>https://www.indeed.com/viewjob?jk=1164a9e1e0387fdf</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-2</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>HealthTronics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be8d80e3db1ec37c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc5df17bcfce4703</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, DevOps</t>
+          <t>Software Architect – Healthcare AI &amp; Cloud Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TransCore</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Round Rock, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae1383c636ae49c</t>
+          <t>https://www.indeed.com/viewjob?jk=13277bedf9c975f6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analytics Architect</t>
+          <t>New College Grad - Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SysLogic, Inc.</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, NoSQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88adb284a479dd50</t>
+          <t>https://www.indeed.com/viewjob?jk=1cfb93ed65fbd759</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Java Software Engineer</t>
+          <t>Software Engineer II - AI Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Oracle, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f79db46ebbc9c81b</t>
+          <t>https://www.indeed.com/viewjob?jk=43c47f699ab58bbd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RWE</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, ETL, CI/CD, Azure DevOps, Terraform, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Spark, PySpark, PostgreSQL, ELT, Power BI, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf874fcd29625031</t>
+          <t>https://www.indeed.com/viewjob?jk=3dce1cb75163081c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer (Job ID 3021796)</t>
+          <t>Data Engineer Snowflake/Agentic AI</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Valtech Group</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Tableau, DataOps, MLOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a7d2b2bb41cc0fe</t>
+          <t>https://www.indeed.com/viewjob?jk=6ebf36281f9e5d65</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Horizon Hobby LLC</t>
+          <t>Credit One Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Champaign, IL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, EMR, Redshift, RDS, Spark, Scala, Kafka, NoSQL, Tableau, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a4c7147702d5d61</t>
+          <t>https://www.indeed.com/viewjob?jk=13b3516dfc64a416</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Data Warehouse Analyst</t>
+          <t>Data Engineer 1, Operational Technology - Operations #4941</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>GRAIL</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f30daf0e86272c78</t>
+          <t>https://www.indeed.com/viewjob?jk=56579d987cf3d3ab</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Warehouse Analyst</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,94 +2211,94 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49dcfa58d40c3abb</t>
+          <t>https://www.indeed.com/viewjob?jk=235a31caf915f203</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NationsBenefits</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca4dfb0e7ccd153c</t>
+          <t>https://www.indeed.com/viewjob?jk=375c331d3616c79b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. QA Analyst</t>
+          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ignite Insurance Systems</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Woburn, MA, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, Power BI, Tableau, CI/CD</t>
+          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83f68e58416a70ba</t>
+          <t>https://www.indeed.com/viewjob?jk=90158ba06c45fb12</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer 1, Operational Technology - Operations #4941</t>
+          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GRAIL</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Troy, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56579d987cf3d3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=b25e04a518ccf371</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ADT</t>
+          <t>Syndeo, LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, Tableau, DataOps, MLOps, CI/CD, Airflow</t>
+          <t>RDS, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT, Docker, Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7cd3f9e08caad2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=872005dc813ce514</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Senior Specialist - Data Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235a31caf915f203</t>
+          <t>https://www.indeed.com/viewjob?jk=9dea3024af69a078</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Department Of Public Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Snowflake, SQL Server, ETL, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f7976cb1e54d6a15</t>
+          <t>https://www.indeed.com/viewjob?jk=576601d5caea8556</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Associate Software Engineer--SAP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Greensboro, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, PostgreSQL, CI/CD, Terraform, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5757314c4e84a8bc</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd3ce8f1ceffdfc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=375c331d3616c79b</t>
+          <t>https://www.indeed.com/viewjob?jk=37d94fa597ec855f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90158ba06c45fb12</t>
+          <t>https://www.indeed.com/viewjob?jk=07441f138a32e7e7</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Cloud DevOps Engineer (AWS | Kubernetes | Terraform)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25e04a518ccf371</t>
+          <t>https://www.indeed.com/viewjob?jk=806a54fa3613e0a5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Microbiologist IV (Genomic Data Engineer)</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Seneca Holdings, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, HDFS, Hive, Impala, Spark, Scala, ETL, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52da99c6b639f191</t>
+          <t>https://www.indeed.com/viewjob?jk=59ae74fce61007b4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Snowflake Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1395ced7e9246546</t>
+          <t>https://www.indeed.com/viewjob?jk=95f514d241530503</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer, Data, AI &amp; UX</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ENGELHART</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Athena, S3, SQS, ECS, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd3a1157126f827c</t>
+          <t>https://www.indeed.com/viewjob?jk=c2569732a012bd1c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Syndeo, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Snowflake, Dimensional Modeling, ETL, ELT, Docker, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=872005dc813ce514</t>
+          <t>https://www.indeed.com/viewjob?jk=44e2ef8c80f8d239</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Associate Software Engineer--SAP</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd3ce8f1ceffdfc</t>
+          <t>https://www.indeed.com/viewjob?jk=a998218acbd3b8e9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer III – Sales, Strategy &amp; Corporate Development</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, RDS, Scala, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f8c9ba81c3d1ed</t>
+          <t>https://www.indeed.com/viewjob?jk=057ed5d0ef018587</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Gen AI Sr. Engineer (Vertex AI / Python / ADK)</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Clever Care Health Plan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, Scala, SQL Server, MySQL, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80c9b7695a5c083</t>
+          <t>https://www.indeed.com/viewjob?jk=fda7cca7efaa2b4a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37d94fa597ec855f</t>
+          <t>https://www.indeed.com/viewjob?jk=144d376d71f5a569</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07441f138a32e7e7</t>
+          <t>https://www.indeed.com/viewjob?jk=1a12d319275ed2e2</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806a54fa3613e0a5</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3cb07a13330396</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59ae74fce61007b4</t>
+          <t>https://www.indeed.com/viewjob?jk=136d8f78fd006971</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Columbia, MD, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95f514d241530503</t>
+          <t>https://www.indeed.com/viewjob?jk=a8f2736a3fb27f5c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2569732a012bd1c</t>
+          <t>https://www.indeed.com/viewjob?jk=33dec0fb23b87e90</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Salesforce Developer (US-Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,182 +3041,182 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44e2ef8c80f8d239</t>
+          <t>https://www.indeed.com/viewjob?jk=0bae9c23ab2afa14</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Senior Full-Stack Software Engineer (Python / React)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, Docker, Kubernetes, AKS, pytest, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a998218acbd3b8e9</t>
+          <t>https://www.indeed.com/viewjob?jk=546d094000822781</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>AECOM</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Power BI, Tableau, MLOps, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=057ed5d0ef018587</t>
+          <t>https://www.indeed.com/viewjob?jk=6f1efae92e327259</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Database Administrator / Data Engineer (12 Month Project)-2</t>
+          <t>Snowflake Data Engineer + Junior Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>University Of Washington</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Data Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b6b9e81dcac42cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bbb6fd4e548ca5c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Level III Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Clever Care Health Plan</t>
+          <t>Blue Margin</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Collins, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Scala, SQL Server, MySQL, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Spark, PySpark, Scala, Snowflake, Data Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fda7cca7efaa2b4a</t>
+          <t>https://www.indeed.com/viewjob?jk=438120063eef4706</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=144d376d71f5a569</t>
+          <t>https://www.indeed.com/viewjob?jk=d64c7ce538beb2b5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>On-call Software Engineer, Cloud Data Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>ICF</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,67 +3261,67 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a12d319275ed2e2</t>
+          <t>https://www.indeed.com/viewjob?jk=817bd6fa9a1fc686</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data System Engineer DevOps</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Franciscan Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mishawaka, IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Databricks, Scala, SQL Server, Power BI, Tableau, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3cb07a13330396</t>
+          <t>https://www.indeed.com/viewjob?jk=9c21057690fd9550</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Senior .NET Software Engineer - MSSQL Database Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>Red Hawk Technologies</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=136d8f78fd006971</t>
+          <t>https://www.indeed.com/viewjob?jk=ccf279671859ea1b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Software Engineer III- Java/Python, SQL, Databricks</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Columbia, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8f2736a3fb27f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce1c0a592c7badc3</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Salesforce Developer (US-Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tenable</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+          <t>S3, RDS, Databricks, Scala, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,567 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33dec0fb23b87e90</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Salesforce Developer (US-Remote)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Tenable</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bae9c23ab2afa14</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Developer &amp; Data Process Engineer (Entry-level)</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Docker, Airflow</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dff0f3ed41fd9d0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>On-call Software Engineer, Cloud Data Platform</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>ICF</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, SQL Server, PostgreSQL, Data Modeling, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=817bd6fa9a1fc686</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Innovation Engineer- Remote (Anywhere in the U.S.)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>GuidePoint Security</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, DynamoDB, MLOps, Terraform, AWS CloudFormation</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c2717547230f0b2</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Data &amp; Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Mankato Clinic</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Mankato, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, Oracle, SQL Server, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35ca511d20adfc77</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer SQL</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Valtech Group</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Spark, Kafka, SQL Server, PostgreSQL, Terraform</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01ecd788ad558b31</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>SDN Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f0147db9614391e</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>SDN Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=045f93f9a84c712a</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>SDN Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d13f2df622bd87a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>SDN Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>AIG GLOBAL OPERATIONS, INC.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=774dd94ebecb0e82</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior .NET Software Engineer - MSSQL Database Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Red Hawk Technologies</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ccf279671859ea1b</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>S3, RDS, Databricks, Scala, MySQL, Data Modeling, ETL, ELT, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=15033510034f9278</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Full Stack .NET Engineer</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e48d48c8e84a2951</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>IT DEVELOPER</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>First Horizon Bank</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ad5bb41689c0fd71</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Google Cloud Platform, Scala, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3b84353b55cf1a47</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Omada Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, S3, SQS, RDS, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d29a16838173b88b</t>
         </is>
       </c>
     </row>
